--- a/artfynd/A 43767-2026 artfynd.xlsx
+++ b/artfynd/A 43767-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297936</v>
+        <v>137545400</v>
       </c>
       <c r="B6" t="n">
-        <v>81312</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626434</v>
+        <v>626135</v>
       </c>
       <c r="R6" t="n">
-        <v>6991055</v>
+        <v>6990759</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,12 +1181,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,27 +1211,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297936</t>
+          <t>https://artportalen.se/Sighting/137545400</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297395</v>
+        <v>129297936</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,38 +1239,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>LÃ¶vsjÃ¶udden, Ång</t>
+          <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626536</v>
+        <v>626434</v>
       </c>
       <c r="R7" t="n">
-        <v>6991090</v>
+        <v>6991055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,22 +1293,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,24 +1313,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297395</t>
+          <t>https://artportalen.se/Sighting/129297936</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129297396</v>
+        <v>129297395</v>
       </c>
       <c r="B8" t="n">
         <v>91909</v>
@@ -1373,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626440</v>
+        <v>626536</v>
       </c>
       <c r="R8" t="n">
-        <v>6991011</v>
+        <v>6991090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1418,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,13 +1440,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297396</t>
+          <t>https://artportalen.se/Sighting/129297395</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297399</v>
+        <v>129297396</v>
       </c>
       <c r="B9" t="n">
         <v>91909</v>
@@ -1489,13 +1485,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626385</v>
+        <v>626440</v>
       </c>
       <c r="R9" t="n">
-        <v>6990959</v>
+        <v>6991011</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,13 +1556,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297399</t>
+          <t>https://artportalen.se/Sighting/129297396</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297402</v>
+        <v>129297399</v>
       </c>
       <c r="B10" t="n">
         <v>91909</v>
@@ -1605,13 +1601,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626436</v>
+        <v>626385</v>
       </c>
       <c r="R10" t="n">
-        <v>6990906</v>
+        <v>6990959</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,13 +1672,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297402</t>
+          <t>https://artportalen.se/Sighting/129297399</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297409</v>
+        <v>129297402</v>
       </c>
       <c r="B11" t="n">
         <v>91909</v>
@@ -1717,17 +1713,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SjÃ¶botten, Ång</t>
+          <t>LÃ¶vsjÃ¶udden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626299</v>
+        <v>626436</v>
       </c>
       <c r="R11" t="n">
-        <v>6990736</v>
+        <v>6990906</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,13 +1788,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297409</t>
+          <t>https://artportalen.se/Sighting/129297402</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297412</v>
+        <v>129297409</v>
       </c>
       <c r="B12" t="n">
         <v>91909</v>
@@ -1837,13 +1833,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626166</v>
+        <v>626299</v>
       </c>
       <c r="R12" t="n">
-        <v>6990918</v>
+        <v>6990736</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1882,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,13 +1904,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297412</t>
+          <t>https://artportalen.se/Sighting/129297409</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297413</v>
+        <v>129297412</v>
       </c>
       <c r="B13" t="n">
         <v>91909</v>
@@ -1953,10 +1949,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626115</v>
+        <v>626166</v>
       </c>
       <c r="R13" t="n">
-        <v>6990999</v>
+        <v>6990918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,7 +1984,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1994,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,13 +2020,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297413</t>
+          <t>https://artportalen.se/Sighting/129297412</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297934</v>
+        <v>129297413</v>
       </c>
       <c r="B14" t="n">
         <v>91909</v>
@@ -2058,17 +2054,21 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lövsjöhöjden, Ång</t>
+          <t>SjÃ¶botten, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626528</v>
+        <v>626115</v>
       </c>
       <c r="R14" t="n">
-        <v>6991106</v>
+        <v>6990999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,12 +2095,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,49 +2125,49 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297934</t>
+          <t>https://artportalen.se/Sighting/129297413</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129297945</v>
+        <v>129297934</v>
       </c>
       <c r="B15" t="n">
-        <v>92083</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2167,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626193</v>
+        <v>626528</v>
       </c>
       <c r="R15" t="n">
-        <v>6991115</v>
+        <v>6991106</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,38 +2238,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297945</t>
+          <t>https://artportalen.se/Sighting/129297934</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129297940</v>
+        <v>129297945</v>
       </c>
       <c r="B16" t="n">
-        <v>91962</v>
+        <v>92083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626427</v>
+        <v>626193</v>
       </c>
       <c r="R16" t="n">
-        <v>6991071</v>
+        <v>6991115</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,38 +2340,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297940</t>
+          <t>https://artportalen.se/Sighting/129297945</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129297946</v>
+        <v>129297940</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>91962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626182</v>
+        <v>626427</v>
       </c>
       <c r="R17" t="n">
-        <v>6991111</v>
+        <v>6991071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,54 +2442,57 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297946</t>
+          <t>https://artportalen.se/Sighting/129297940</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129297937</v>
+        <v>137545394</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>92152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626434</v>
+        <v>626295</v>
       </c>
       <c r="R18" t="n">
-        <v>6991055</v>
+        <v>6990666</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,12 +2516,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>kolad kärnved som substrat.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,53 +2547,68 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297937</t>
+          <t>https://artportalen.se/Sighting/137545394</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297938</v>
+        <v>137545398</v>
       </c>
       <c r="B19" t="n">
-        <v>79413</v>
+        <v>92152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2575,13 +2618,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626429</v>
+        <v>626234</v>
       </c>
       <c r="R19" t="n">
-        <v>6991071</v>
+        <v>6990766</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2605,12 +2648,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,69 +2678,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297938</t>
+          <t>https://artportalen.se/Sighting/137545398</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297400</v>
+        <v>137545399</v>
       </c>
       <c r="B20" t="n">
-        <v>80432</v>
+        <v>92152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>LÃ¶vsjÃ¶udden, Ång</t>
+          <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626340</v>
+        <v>626147</v>
       </c>
       <c r="R20" t="n">
-        <v>6990949</v>
+        <v>6990753</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2711,22 +2760,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,66 +2790,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297400</t>
+          <t>https://artportalen.se/Sighting/137545399</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129297401</v>
+        <v>137546760</v>
       </c>
       <c r="B21" t="n">
-        <v>80432</v>
+        <v>92152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>LÃ¶vsjÃ¶udden, Ång</t>
+          <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626387</v>
+        <v>626181</v>
       </c>
       <c r="R21" t="n">
-        <v>6990913</v>
+        <v>6990814</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2827,22 +2875,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,72 +2899,84 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297401</t>
+          <t>https://artportalen.se/Sighting/137546760</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129297408</v>
+        <v>129297946</v>
       </c>
       <c r="B22" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>LÃ¶vsjÃ¶udden, Ång</t>
+          <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626316</v>
+        <v>626182</v>
       </c>
       <c r="R22" t="n">
-        <v>6990867</v>
+        <v>6991111</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2943,22 +3003,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2973,69 +3023,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297408</t>
+          <t>https://artportalen.se/Sighting/129297946</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129297415</v>
+        <v>137545408</v>
       </c>
       <c r="B23" t="n">
-        <v>80432</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>SjÃ¶botten, Ång</t>
+          <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626034</v>
+        <v>626368</v>
       </c>
       <c r="R23" t="n">
-        <v>6991061</v>
+        <v>6991091</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3059,22 +3108,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3083,71 +3132,90 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297415</t>
+          <t>https://artportalen.se/Sighting/137545408</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297944</v>
+        <v>137546758</v>
       </c>
       <c r="B24" t="n">
-        <v>80432</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626289</v>
+        <v>626221</v>
       </c>
       <c r="R24" t="n">
-        <v>6991048</v>
+        <v>6990735</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3171,12 +3239,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3185,72 +3263,84 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297944</t>
+          <t>https://artportalen.se/Sighting/137546758</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297398</v>
+        <v>129297937</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>LÃ¶vsjÃ¶udden, Ång</t>
+          <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626462</v>
+        <v>626434</v>
       </c>
       <c r="R25" t="n">
-        <v>6990943</v>
+        <v>6991055</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3277,22 +3367,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3307,69 +3387,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297398</t>
+          <t>https://artportalen.se/Sighting/129297937</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129297403</v>
+        <v>129297938</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>79413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>LÃ¶vsjÃ¶udden, Ång</t>
+          <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626456</v>
+        <v>626429</v>
       </c>
       <c r="R26" t="n">
-        <v>6990917</v>
+        <v>6991071</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3393,22 +3469,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,69 +3489,68 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297403</t>
+          <t>https://artportalen.se/Sighting/129297938</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129297406</v>
+        <v>137545396</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>80548</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>LÃ¶vsjÃ¶udden, Ång</t>
+          <t>Lövsjöhöjden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626434</v>
+        <v>626244</v>
       </c>
       <c r="R27" t="n">
-        <v>6990858</v>
+        <v>6990757</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3509,22 +3574,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,69 +3600,88 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297406</t>
+          <t>https://artportalen.se/Sighting/137545396</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129297939</v>
+        <v>129297400</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövsjöhöjden, Ång</t>
+          <t>LÃ¶vsjÃ¶udden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626427</v>
+        <v>626340</v>
       </c>
       <c r="R28" t="n">
-        <v>6991071</v>
+        <v>6990949</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3621,12 +3705,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3641,65 +3735,69 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297939</t>
+          <t>https://artportalen.se/Sighting/129297400</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129297941</v>
+        <v>129297401</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövsjöhöjden, Ång</t>
+          <t>LÃ¶vsjÃ¶udden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626308</v>
+        <v>626387</v>
       </c>
       <c r="R29" t="n">
-        <v>6991047</v>
+        <v>6990913</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3723,12 +3821,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3743,62 +3851,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129297941</t>
+          <t>https://artportalen.se/Sighting/129297401</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129297943</v>
+        <v>129297408</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövsjöhöjden, Ång</t>
+          <t>LÃ¶vsjÃ¶udden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626289</v>
+        <v>626316</v>
       </c>
       <c r="R30" t="n">
-        <v>6991048</v>
+        <v>6990867</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3825,12 +3937,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,18 +3967,3738 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/129297408</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129297415</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SjÃ¶botten, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>626034</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6991061</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297415</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129297944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>626289</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6991048</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297944</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137545403</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80654</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>626107</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6990828</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545403</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137545407</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>626264</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6991031</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545407</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137546759</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>626241</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6990778</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546759</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137546761</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>626174</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6990754</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546761</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137546762</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>626131</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6990767</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546762</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137546767</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>626373</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6991093</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546767</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137546770</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>626585</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6991109</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546770</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137545397</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>626230</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6990753</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545397</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137545401</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626139</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6990792</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545401</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137545409</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>626413</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6991092</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545409</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137546756</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626280</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6990685</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546756</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137546757</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>626266</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6990692</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546757</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137546766</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>626373</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6991093</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546766</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137546768</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>626505</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6991116</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546768</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137545404</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58199</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>626101</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6990906</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545404</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137545410</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58199</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>626440</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6991119</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545410</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137545395</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>626219</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6990675</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545395</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137545411</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>626526</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6991119</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545411</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137546765</v>
+      </c>
+      <c r="B51" t="n">
+        <v>111436</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>626208</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6991032</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546765</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129297398</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>LÃ¶vsjÃ¶udden, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>626462</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6990943</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297398</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129297403</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>LÃ¶vsjÃ¶udden, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>626456</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6990917</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297403</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129297406</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>LÃ¶vsjÃ¶udden, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>626434</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6990858</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297406</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129297939</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>626427</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6991071</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297939</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129297941</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>626308</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6991047</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297941</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129297943</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>626289</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6991048</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129297943</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137545406</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>626151</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6990955</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545406</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137545412</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>626600</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6991080</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545412</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137546763</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>626107</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6990834</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546763</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137545405</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>626074</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6990955</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137545405</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137546764</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lövsjöhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>626124</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6990846</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Dal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137546764</t>
         </is>
       </c>
     </row>
@@ -3891,6 +7733,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
